--- a/game28/web.xlsx
+++ b/game28/web.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15000" windowHeight="7620" activeTab="1"/>
+    <workbookView windowWidth="16245" windowHeight="11745"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet3" sheetId="14" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="15" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="13" r:id="rId3"/>
-    <sheet name="Sheet5" sheetId="10" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,154 +35,168 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>domain</t>
   </si>
   <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>color2</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>ethere.site</t>
+  </si>
+  <si>
+    <t>#ba8677</t>
+  </si>
+  <si>
+    <t>#549688</t>
+  </si>
+  <si>
+    <t>iridize.site</t>
+  </si>
+  <si>
+    <t>#ddd23b</t>
+  </si>
+  <si>
+    <t>#82f0f9</t>
+  </si>
+  <si>
+    <t>auroral.site</t>
+  </si>
+  <si>
+    <t>#a7dbc8</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>read.newsdesk.fun</t>
+  </si>
+  <si>
+    <t>#664b3a</t>
+  </si>
+  <si>
+    <t>#fb9966</t>
+  </si>
+  <si>
+    <t>sec.newsdesk.fun</t>
+  </si>
+  <si>
+    <t>template</t>
+  </si>
+  <si>
     <t>color</t>
   </si>
   <si>
-    <t>color2</t>
-  </si>
-  <si>
-    <t>sec.wuuui.top</t>
-  </si>
-  <si>
-    <t>#957aa9</t>
-  </si>
-  <si>
-    <t>sec.flowflux.cloud</t>
-  </si>
-  <si>
-    <t>#33325d</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>color1</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>lagoonsea.com</t>
-  </si>
-  <si>
-    <t>#ffc408</t>
-  </si>
-  <si>
-    <t>navyseas.com</t>
-  </si>
-  <si>
-    <t>#6b496a</t>
-  </si>
-  <si>
-    <t>sapphsea.com</t>
-  </si>
-  <si>
-    <t>#e6e3c3</t>
-  </si>
-  <si>
-    <t>skyssea.com</t>
-  </si>
-  <si>
-    <t>#606da1</t>
-  </si>
-  <si>
-    <t>sunseabc.com</t>
-  </si>
-  <si>
-    <t>#ee819e</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF175CEB"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>sec</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF175CEB"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.desertwoodrat.com</t>
-    </r>
-  </si>
-  <si>
-    <t>#fdf4e3</t>
-  </si>
-  <si>
-    <t>#7c8d99</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF175CEB"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>sec</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF175CEB"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.desertskink.com</t>
-    </r>
-  </si>
-  <si>
-    <t>#e1e6e9</t>
-  </si>
-  <si>
-    <t>#a35e5e</t>
-  </si>
-  <si>
-    <t>sec.eunoias.cloud</t>
-  </si>
-  <si>
-    <t>#f0ff31</t>
-  </si>
-  <si>
-    <t>sec.uminous.top</t>
-  </si>
-  <si>
-    <t>#27456c</t>
-  </si>
-  <si>
-    <t>sec.nebulous.top</t>
-  </si>
-  <si>
-    <t>#98b0ca</t>
+    <t>game53</t>
+  </si>
+  <si>
+    <t>play.roadoffset.cloud</t>
+  </si>
+  <si>
+    <t>#1c579b</t>
+  </si>
+  <si>
+    <t>sec.roadoffset.cloud</t>
+  </si>
+  <si>
+    <t>#003153</t>
+  </si>
+  <si>
+    <t>play.frontages.site</t>
+  </si>
+  <si>
+    <t>#dfbc1f</t>
+  </si>
+  <si>
+    <t>sec.frontages.site</t>
+  </si>
+  <si>
+    <t>#284fef</t>
+  </si>
+  <si>
+    <t>game18</t>
+  </si>
+  <si>
+    <t>play.medianbar.fun</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>sec.medianbar.fun</t>
+  </si>
+  <si>
+    <t>#b65458</t>
+  </si>
+  <si>
+    <t>game28</t>
+  </si>
+  <si>
+    <t>play.sunseabc.com</t>
+  </si>
+  <si>
+    <t>#f53d93</t>
+  </si>
+  <si>
+    <t>sec.sunseabc.com</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>周一</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>周六</t>
+  </si>
+  <si>
+    <t>周日</t>
+  </si>
+  <si>
+    <t>早餐</t>
+  </si>
+  <si>
+    <t>板栗</t>
+  </si>
+  <si>
+    <t>午餐</t>
+  </si>
+  <si>
+    <t>意面+生菜+鸡胸肉丸</t>
+  </si>
+  <si>
+    <t>晚餐</t>
+  </si>
+  <si>
+    <t>一个鸡蛋，一根玉米</t>
+  </si>
+  <si>
+    <t>havenlyspaces.net</t>
+  </si>
+  <si>
+    <t>adcloud-culture.com</t>
   </si>
 </sst>
 </file>
@@ -199,6 +218,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF2972F4"/>
@@ -208,35 +242,14 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF175CEB"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -249,8 +262,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -265,28 +313,6 @@
     </font>
     <font>
       <u/>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF1450B8"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
@@ -421,16 +447,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF175CEB"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="52">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,103 +457,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0FF31"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27456C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98B0CA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7C8D99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1E6E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA35E5E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD0C4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC408"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6090B8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6B496A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6E3C3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF606DA1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE819E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF957AA9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA61B29"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33325D"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C579B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -547,7 +475,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF70C588"/>
+        <fgColor rgb="FF003153"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFBC1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE58889"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF284FEF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDBB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB65458"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF53D93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF664B3A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFB9966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA8677"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF549688"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD23B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82F0F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -738,21 +744,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFE3E4E6"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -871,64 +868,70 @@
     <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -937,10 +940,10 @@
     <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -949,10 +952,10 @@
     <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -961,10 +964,10 @@
     <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -973,10 +976,10 @@
     <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -985,114 +988,120 @@
     <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1147,6 +1156,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F4F207"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1477,13 +1491,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="27.75" customWidth="1"/>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1493,62 +1507,96 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="26"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="26"/>
-    </row>
-    <row r="4" ht="15" spans="1:7">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-    </row>
-    <row r="5" ht="15" spans="1:7">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-    </row>
-    <row r="6" ht="15" spans="1:7">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="F16" s="29" t="s">
+      <c r="C2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="D2" s="14">
+        <v>1</v>
+      </c>
+      <c r="E2" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="31" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="6:7">
-      <c r="F17" s="29" t="s">
+      <c r="B3" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="C3" s="35" t="s">
         <v>10</v>
       </c>
+      <c r="D3" s="14">
+        <v>2</v>
+      </c>
+      <c r="E3" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="14">
+        <v>3</v>
+      </c>
+      <c r="E4" s="14">
+        <v>5</v>
+      </c>
+      <c r="F4" s="29"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="29"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="37"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="29"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="29"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="29"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
-    <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
-    <hyperlink ref="A6" r:id="rId3" tooltip="https://jentacul.com"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1557,131 +1605,247 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="28.75" customWidth="1"/>
+    <col min="4" max="4" width="9.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="13">
+        <v>46273</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="18"/>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:6">
-      <c r="A5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="18"/>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5" s="15">
-        <v>5</v>
-      </c>
-      <c r="F5" s="22"/>
-    </row>
-    <row r="6" ht="15" spans="1:6">
-      <c r="A6" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6" s="15">
-        <v>5</v>
-      </c>
-      <c r="F6" s="22"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="D7" s="15"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="D8" s="15"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="D9" s="15"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="D10" s="15"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="D11" s="15"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="D12" s="15"/>
+      <c r="D3" s="13">
+        <v>46303</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="30"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="lagoonsea.com" tooltip="https://lagoonsea.com"/>
-    <hyperlink ref="A3" r:id="rId2" display="navyseas.com" tooltip="https://navyseas.com"/>
-    <hyperlink ref="A4" r:id="rId3" display="sapphsea.com" tooltip="https://sapphsea.com"/>
-    <hyperlink ref="A5" r:id="rId4" display="skyssea.com" tooltip="https://skyssea.com"/>
-    <hyperlink ref="A6" r:id="rId5" display="sunseabc.com" tooltip="https://sunseabc.com"/>
+    <hyperlink ref="A10" r:id="rId1"/>
+    <hyperlink ref="A11" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1691,87 +1855,316 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.375" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="27.75" customWidth="1"/>
+    <col min="5" max="5" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
       <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
       </c>
       <c r="E1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="7" t="s">
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="14">
+        <v>1</v>
+      </c>
+      <c r="G2" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14">
+        <v>2</v>
+      </c>
+      <c r="G3" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:9">
+      <c r="A4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D2">
+      <c r="D4" s="17"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14">
+        <v>3</v>
+      </c>
+      <c r="G4" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14">
+        <v>4</v>
+      </c>
+      <c r="G5" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14">
+        <v>5</v>
+      </c>
+      <c r="G6" s="14">
+        <v>6</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="14">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="14">
+        <v>3</v>
+      </c>
+      <c r="G9" s="14">
+        <v>7</v>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="25"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="E21" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1"/>
-    <hyperlink ref="A2" r:id="rId2" display="sec.desertwoodrat.com" tooltip="http://desertwoodrat.com"/>
-    <hyperlink ref="A3" r:id="rId3" display="sec.desertskink.com" tooltip="http://desertskink.com"/>
+    <hyperlink ref="G16" r:id="rId1"/>
+    <hyperlink ref="G17" r:id="rId2"/>
+    <hyperlink ref="B8" r:id="rId3" display="play.sunseabc.com"/>
+    <hyperlink ref="B9" r:id="rId3" display="sec.sunseabc.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1781,102 +2174,117 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="22.375" customWidth="1"/>
+    <col min="5" max="5" width="22.625" customWidth="1"/>
+    <col min="6" max="6" width="24.25" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="C7" s="6"/>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="1:8">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" ht="52" customHeight="1" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" ht="74" customHeight="1" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" ht="100" customHeight="1" spans="1:8">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="C11" s="7"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1"/>
-    <hyperlink ref="A6" r:id="rId2"/>
-    <hyperlink ref="B5" r:id="rId1"/>
-    <hyperlink ref="C5" r:id="rId1"/>
-    <hyperlink ref="D5" r:id="rId1"/>
-    <hyperlink ref="E5" r:id="rId1"/>
-    <hyperlink ref="B6" r:id="rId2"/>
-    <hyperlink ref="C6" r:id="rId2"/>
-    <hyperlink ref="D6" r:id="rId2"/>
-    <hyperlink ref="E6" r:id="rId2"/>
-  </hyperlinks>
+  <mergeCells count="1">
+    <mergeCell ref="A3:A4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
